--- a/data/WOP_2026_planning.xlsx
+++ b/data/WOP_2026_planning.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pth7\Documents\Intercrop JLJ\2026_winter\2026_winter\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58999C61-2167-47B2-88A8-C8077B337CA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADE23EE5-08B0-4D56-89A6-3615AFB75522}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="28800" windowHeight="15285" activeTab="5" xr2:uid="{D40C415E-5EC6-489A-8663-B1D283C6BF70}"/>
+    <workbookView xWindow="585" yWindow="45" windowWidth="31620" windowHeight="20745" xr2:uid="{D40C415E-5EC6-489A-8663-B1D283C6BF70}"/>
   </bookViews>
   <sheets>
     <sheet name="original" sheetId="1" r:id="rId1"/>
